--- a/quizzes/peinture-20e.xlsx
+++ b/quizzes/peinture-20e.xlsx
@@ -1416,7 +1416,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>c.1913</t>
+          <t>environ 1913</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>c.1922</t>
+          <t>environ 1922</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>c.1925</t>
+          <t>environ 1925</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>c.1900</t>
+          <t>environ 1900</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>c.1919</t>
+          <t>environ 1919</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>c.1930</t>
+          <t>environ 1930</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>c.1905-1906</t>
+          <t>environ 1905-1906</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>c.1919</t>
+          <t>environ 1919</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>c.1918</t>
+          <t>environ 1918</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">

--- a/quizzes/peinture-20e.xlsx
+++ b/quizzes/peinture-20e.xlsx
@@ -2172,7 +2172,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>environ 1913</t>
+          <t>1913 environ</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>environ 1922</t>
+          <t>1922 environ</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>environ 1919</t>
+          <t>1919 environ</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>environ 1919</t>
+          <t>1919 environ</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>environ 1900</t>
+          <t>1900 environ</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>environ 1930</t>
+          <t>1930 environ</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>environ 1925</t>
+          <t>1925 environ</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>environ 1905-1906</t>
+          <t>1905-1906 environ</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>environ 1918</t>
+          <t>1918 environ</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
